--- a/examples/customer-sync/客户主表.xlsx
+++ b/examples/customer-sync/客户主表.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -73,16 +74,16 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,11 +454,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
